--- a/DATA MASTER KONTRAK NO '7207250142.xlsx
+++ b/DATA MASTER KONTRAK NO '7207250142.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6629804D-F622-4DD4-8DEC-5AFF31936AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD39E97F-D247-41C6-8792-EF2A8EB4B503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,27 +801,12 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Kategory</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Qty</t>
   </si>
   <si>
     <t>Unit</t>
   </si>
   <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Total Price</t>
-  </si>
-  <si>
     <t>MONTHLY BASIS</t>
   </si>
   <si>
@@ -913,6 +898,21 @@
   </si>
   <si>
     <t>No Kontrak</t>
+  </si>
+  <si>
+    <t>Harga Satuan</t>
+  </si>
+  <si>
+    <t>Total Harga</t>
+  </si>
+  <si>
+    <t>Satuan</t>
+  </si>
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Spesifikasi / Deskripsi Pekerjaan </t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
     <numFmt numFmtId="164" formatCode="_([$Rp-421]* #,##0_);_([$Rp-421]* \(#,##0\);_([$Rp-421]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -996,6 +996,12 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1132,7 +1138,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="6" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1186,6 +1192,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="Comma [0] 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
@@ -1626,13 +1635,13 @@
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No." dataDxfId="9" dataCellStyle="Normal 3 3"/>
     <tableColumn id="8" xr3:uid="{EE801E05-357E-44F3-A601-DC0237DBA5BC}" name="No Kontrak" dataDxfId="8" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Kategory" dataDxfId="7" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Description" dataDxfId="6" dataCellStyle="Normal 14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Kategori" dataDxfId="7" dataCellStyle="Normal 3 3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spesifikasi / Deskripsi Pekerjaan " dataDxfId="6" dataCellStyle="Normal 14"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Qty" dataDxfId="5" dataCellStyle="Normal 3 3"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Unit" dataDxfId="4" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Rate" dataDxfId="3" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Unit Price" dataDxfId="2" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Total Price" dataDxfId="1" dataCellStyle="Normal 3 3">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Satuan" dataDxfId="3" dataCellStyle="Normal 3 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Harga Satuan" dataDxfId="2" dataCellStyle="Normal 3 3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Total Harga" dataDxfId="1" dataCellStyle="Normal 3 3">
       <calculatedColumnFormula>F2*I2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1951,28 +1960,28 @@
         <v>0</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>4</v>
-      </c>
       <c r="H1" s="18" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="2:10" ht="33.85" customHeight="1" x14ac:dyDescent="0.35">
@@ -1983,19 +1992,19 @@
         <v>7207250142</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3">
         <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I2" s="4">
         <v>131224000</v>
@@ -2013,19 +2022,19 @@
         <v>7207250142</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3">
         <v>36</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I3" s="4">
         <v>62818000</v>
@@ -2043,19 +2052,19 @@
         <v>7207250142</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F4" s="3">
         <v>36</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I4" s="4">
         <v>189241000</v>
@@ -2073,19 +2082,19 @@
         <v>7207250142</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>8</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>13</v>
       </c>
       <c r="F5" s="3">
         <v>36</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" s="4">
         <v>75538000</v>
@@ -2103,19 +2112,19 @@
         <v>7207250142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F6" s="3">
         <v>36</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I6" s="4">
         <v>78225000</v>
@@ -2133,19 +2142,19 @@
         <v>7207250142</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3">
         <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I7" s="4">
         <v>1936000</v>
@@ -2164,19 +2173,19 @@
         <v>7207250142</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3">
         <v>120</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I8" s="4">
         <v>4746000</v>
@@ -2195,19 +2204,19 @@
         <v>7207250142</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3">
         <v>365</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I9" s="4">
         <v>5340000</v>
@@ -2226,19 +2235,19 @@
         <v>7207250142</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>15</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="F10" s="3">
         <v>365</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I10" s="4">
         <v>4231000</v>
@@ -2257,19 +2266,19 @@
         <v>7207250142</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3">
         <v>60</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I11" s="4">
         <v>2215000</v>
@@ -2288,19 +2297,19 @@
         <v>7207250142</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F12" s="3">
         <v>10</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I12" s="4">
         <v>210000000</v>
@@ -2319,19 +2328,19 @@
         <v>7207250142</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3">
         <v>10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I13" s="4">
         <v>350000000</v>
@@ -2350,19 +2359,19 @@
         <v>7207250142</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F14" s="3">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I14" s="4">
         <v>80000000</v>
@@ -2381,19 +2390,19 @@
         <v>7207250142</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F15" s="3">
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15" s="4">
         <v>75000000</v>
@@ -2411,19 +2420,19 @@
         <v>7207250142</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I16" s="4">
         <v>400000000</v>
@@ -2441,19 +2450,19 @@
         <v>7207250142</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -2471,19 +2480,19 @@
         <v>7207250142</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>26</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>31</v>
       </c>
       <c r="F18" s="3">
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I18" s="4">
         <v>300000000</v>
@@ -2501,19 +2510,19 @@
         <v>7207250142</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
         <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I19" s="4">
         <v>7500000</v>
@@ -2531,19 +2540,19 @@
         <v>7207250142</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3">
         <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I20" s="4">
         <v>7500000</v>
@@ -2561,19 +2570,19 @@
         <v>7207250142</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F21" s="3">
         <v>22</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I21" s="4">
         <v>8500000</v>
@@ -2591,19 +2600,19 @@
         <v>7207250142</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F22" s="12">
         <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I22" s="15">
         <v>3846170660.5</v>

--- a/DATA MASTER KONTRAK NO '7207250142.xlsx
+++ b/DATA MASTER KONTRAK NO '7207250142.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD39E97F-D247-41C6-8792-EF2A8EB4B503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645FA6B3-A551-4F5F-A439-780272D881A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -912,7 +912,7 @@
     <t>Kategori</t>
   </si>
   <si>
-    <t>Spesifikasi / Deskripsi Pekerjaan </t>
+    <t>Spesifikasi / Deskripsi Pekerjaan</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1636,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No." dataDxfId="9" dataCellStyle="Normal 3 3"/>
     <tableColumn id="8" xr3:uid="{EE801E05-357E-44F3-A601-DC0237DBA5BC}" name="No Kontrak" dataDxfId="8" dataCellStyle="Normal 3 3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Kategori" dataDxfId="7" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spesifikasi / Deskripsi Pekerjaan " dataDxfId="6" dataCellStyle="Normal 14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spesifikasi / Deskripsi Pekerjaan" dataDxfId="6" dataCellStyle="Normal 14"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Qty" dataDxfId="5" dataCellStyle="Normal 3 3"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Unit" dataDxfId="4" dataCellStyle="Normal 3 3"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Satuan" dataDxfId="3" dataCellStyle="Normal 3 3"/>

--- a/DATA MASTER KONTRAK NO '7207250142.xlsx
+++ b/DATA MASTER KONTRAK NO '7207250142.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645FA6B3-A551-4F5F-A439-780272D881A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A3B9CC-1357-4D36-9CBA-D0508E847E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,9 +801,6 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Qty</t>
-  </si>
-  <si>
     <t>Unit</t>
   </si>
   <si>
@@ -912,7 +909,10 @@
     <t>Kategori</t>
   </si>
   <si>
-    <t>Spesifikasi / Deskripsi Pekerjaan</t>
+    <t>Uraian Pekerjaan</t>
+  </si>
+  <si>
+    <t>Kwt</t>
   </si>
 </sst>
 </file>
@@ -1636,8 +1636,8 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No." dataDxfId="9" dataCellStyle="Normal 3 3"/>
     <tableColumn id="8" xr3:uid="{EE801E05-357E-44F3-A601-DC0237DBA5BC}" name="No Kontrak" dataDxfId="8" dataCellStyle="Normal 3 3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Kategori" dataDxfId="7" dataCellStyle="Normal 3 3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Spesifikasi / Deskripsi Pekerjaan" dataDxfId="6" dataCellStyle="Normal 14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Qty" dataDxfId="5" dataCellStyle="Normal 3 3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Uraian Pekerjaan" dataDxfId="6" dataCellStyle="Normal 14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Kwt" dataDxfId="5" dataCellStyle="Normal 3 3"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Unit" dataDxfId="4" dataCellStyle="Normal 3 3"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Satuan" dataDxfId="3" dataCellStyle="Normal 3 3"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Harga Satuan" dataDxfId="2" dataCellStyle="Normal 3 3"/>
@@ -1960,28 +1960,28 @@
         <v>0</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>34</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="2:10" ht="33.85" customHeight="1" x14ac:dyDescent="0.35">
@@ -1992,19 +1992,19 @@
         <v>7207250142</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>4</v>
       </c>
       <c r="F2" s="3">
         <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2" s="4">
         <v>131224000</v>
@@ -2022,19 +2022,19 @@
         <v>7207250142</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="3">
         <v>36</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="4">
         <v>62818000</v>
@@ -2052,19 +2052,19 @@
         <v>7207250142</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3">
         <v>36</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="4">
         <v>189241000</v>
@@ -2082,19 +2082,19 @@
         <v>7207250142</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="3">
         <v>36</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4">
         <v>75538000</v>
@@ -2112,19 +2112,19 @@
         <v>7207250142</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="3">
         <v>36</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" s="4">
         <v>78225000</v>
@@ -2142,19 +2142,19 @@
         <v>7207250142</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>10</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>11</v>
       </c>
       <c r="F7" s="3">
         <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I7" s="4">
         <v>1936000</v>
@@ -2173,19 +2173,19 @@
         <v>7207250142</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="3">
         <v>120</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4">
         <v>4746000</v>
@@ -2204,19 +2204,19 @@
         <v>7207250142</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3">
         <v>365</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" s="4">
         <v>5340000</v>
@@ -2235,19 +2235,19 @@
         <v>7207250142</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3">
         <v>365</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4">
         <v>4231000</v>
@@ -2266,19 +2266,19 @@
         <v>7207250142</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3">
         <v>60</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I11" s="4">
         <v>2215000</v>
@@ -2297,19 +2297,19 @@
         <v>7207250142</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3">
         <v>10</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" s="4">
         <v>210000000</v>
@@ -2328,19 +2328,19 @@
         <v>7207250142</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3">
         <v>10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13" s="4">
         <v>350000000</v>
@@ -2359,19 +2359,19 @@
         <v>7207250142</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" s="3">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4">
         <v>80000000</v>
@@ -2390,19 +2390,19 @@
         <v>7207250142</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" s="3">
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="4">
         <v>75000000</v>
@@ -2420,19 +2420,19 @@
         <v>7207250142</v>
       </c>
       <c r="D16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="16" t="s">
         <v>21</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>22</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I16" s="4">
         <v>400000000</v>
@@ -2450,19 +2450,19 @@
         <v>7207250142</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -2480,19 +2480,19 @@
         <v>7207250142</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I18" s="4">
         <v>300000000</v>
@@ -2510,19 +2510,19 @@
         <v>7207250142</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
         <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I19" s="4">
         <v>7500000</v>
@@ -2540,19 +2540,19 @@
         <v>7207250142</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3">
         <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I20" s="4">
         <v>7500000</v>
@@ -2570,19 +2570,19 @@
         <v>7207250142</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3">
         <v>22</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="I21" s="4">
         <v>8500000</v>
@@ -2600,19 +2600,19 @@
         <v>7207250142</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="F22" s="12">
         <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="15">
         <v>3846170660.5</v>

--- a/DATA MASTER KONTRAK NO '7207250142.xlsx
+++ b/DATA MASTER KONTRAK NO '7207250142.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A3B9CC-1357-4D36-9CBA-D0508E847E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB13BF4-5F38-4134-98D1-026F22151AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
